--- a/Results/Two_Datasets_Assessment/Cancer/Tables/overall_scores.xlsx
+++ b/Results/Two_Datasets_Assessment/Cancer/Tables/overall_scores.xlsx
@@ -491,13 +491,13 @@
         <v>0.968362898094103</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2648177399141864</v>
+        <v>0.4849657455036203</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7458789484729241</v>
+        <v>0.7279601106252133</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6905541657537744</v>
+        <v>0.7512229160762912</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -505,7 +505,7 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -514,23 +514,23 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CTABGAN</t>
+          <t>WGAN_GP</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8534899925686222</v>
+        <v>0.9355254935904923</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5133862651733053</v>
+        <v>0.4785157516103453</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5363147907251201</v>
+        <v>0.7262959665789475</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6563063137969766</v>
+        <v>0.7356537128929848</v>
       </c>
       <c r="I3" t="n">
         <v>2</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -547,23 +547,23 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TVAE</t>
+          <t>GaussianCopula</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9230599709384475</v>
+        <v>0.8200940787089187</v>
       </c>
       <c r="F4" t="n">
-        <v>0.413774075177361</v>
+        <v>0.519908292713704</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4877173849809624</v>
+        <v>0.8121587739421542</v>
       </c>
       <c r="H4" t="n">
-        <v>0.639671426422876</v>
+        <v>0.7276577514803249</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -580,23 +580,23 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GaussianCopula</t>
+          <t>TVAE</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8200940787089187</v>
+        <v>0.9230599709384475</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3928241452145236</v>
+        <v>0.5372078162303315</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6147824256659962</v>
+        <v>0.5817496483258702</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6303196027477234</v>
+        <v>0.7049112277422396</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
@@ -604,7 +604,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -613,23 +613,23 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>WGAN_GP</t>
+          <t>CTABGAN</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9355254935904923</v>
+        <v>0.8534899925686222</v>
       </c>
       <c r="F6" t="n">
-        <v>0.255724578002569</v>
+        <v>0.5275669612932169</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5695028378343651</v>
+        <v>0.6670557325674165</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6217784221872772</v>
+        <v>0.699782805185639</v>
       </c>
       <c r="I6" t="n">
         <v>5</v>
@@ -656,13 +656,13 @@
         <v>0.7038964675556111</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4750360720991947</v>
+        <v>0.4872794696822143</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3123008246014149</v>
+        <v>0.2013340430684206</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5177596560324272</v>
+        <v>0.4881426408474349</v>
       </c>
       <c r="I7" t="n">
         <v>6</v>
@@ -689,13 +689,13 @@
         <v>0.3220413157082996</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5143939653183046</v>
+        <v>0.4629545687864741</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4597927818721145</v>
+        <v>0.7201306164880913</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4210725504404456</v>
+        <v>0.4837420818656895</v>
       </c>
       <c r="I8" t="n">
         <v>7</v>
@@ -722,13 +722,13 @@
         <v>0.3729653880480129</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3682877872336551</v>
+        <v>0.493020634446126</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3801171918778428</v>
+        <v>0.1717370163302168</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3737076489526545</v>
+        <v>0.348613450452108</v>
       </c>
       <c r="I9" t="n">
         <v>8</v>
